--- a/reportes/movimientos.xlsx
+++ b/reportes/movimientos.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,51 +427,51 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-12 07:19:19</v>
+        <v>2026-06-13 20:18:04</v>
       </c>
       <c r="C2" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D2" t="str">
-        <v>Pantalon</v>
+        <v>Bata Azul</v>
       </c>
       <c r="E2" t="str">
-        <v>10-12</v>
+        <v>Unica</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="str">
         <v>Administrador</v>
       </c>
       <c r="H2" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-12 06:44:32</v>
+        <v>2026-06-12 07:19:19</v>
       </c>
       <c r="C3" t="str">
         <v>entrada</v>
       </c>
       <c r="D3" t="str">
-        <v>Camisa Gala</v>
+        <v>Pantalon</v>
       </c>
       <c r="E3" t="str">
-        <v>M-L</v>
+        <v>10-12</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="H3" t="str">
         <v>Entrada de stock</v>
@@ -479,36 +479,36 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-12 06:36:20</v>
+        <v>2026-06-12 06:44:32</v>
       </c>
       <c r="C4" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D4" t="str">
-        <v>Pantalon</v>
+        <v>Camisa Gala</v>
       </c>
       <c r="E4" t="str">
-        <v>10-12</v>
+        <v>M-L</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H4" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-12 06:31:22</v>
+        <v>2026-06-12 06:36:20</v>
       </c>
       <c r="C5" t="str">
         <v>venta</v>
@@ -526,12 +526,38 @@
         <v>Administrador</v>
       </c>
       <c r="H5" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>33</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-12 06:31:22</v>
+      </c>
+      <c r="C6" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E6" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="H6" t="str">
         <v>Venta registrada</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/movimientos.xlsx
+++ b/reportes/movimientos.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,39 +427,39 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-13 20:18:04</v>
+        <v>2026-06-17 07:39:58</v>
       </c>
       <c r="C2" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D2" t="str">
-        <v>Bata Azul</v>
+        <v>Pantalon</v>
       </c>
       <c r="E2" t="str">
-        <v>Unica</v>
+        <v>10-12</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H2" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-12 07:19:19</v>
+        <v>2026-06-16 20:39:32</v>
       </c>
       <c r="C3" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D3" t="str">
         <v>Pantalon</v>
@@ -468,50 +468,50 @@
         <v>10-12</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H3" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-12 06:44:32</v>
+        <v>2026-06-16 20:39:20</v>
       </c>
       <c r="C4" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D4" t="str">
-        <v>Camisa Gala</v>
+        <v>Pantalon</v>
       </c>
       <c r="E4" t="str">
-        <v>M-L</v>
+        <v>10-12</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H4" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-12 06:36:20</v>
+        <v>2026-06-16 19:42:36</v>
       </c>
       <c r="C5" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D5" t="str">
         <v>Pantalon</v>
@@ -520,44 +520,408 @@
         <v>10-12</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H5" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
+        <v>47</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-16 19:42:27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>46</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-16 16:32:55</v>
+      </c>
+      <c r="C7" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Bata Manga Larga</v>
+      </c>
+      <c r="E7" t="str">
+        <v>M-L</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>43</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-16 16:22:12</v>
+      </c>
+      <c r="C8" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Buso</v>
+      </c>
+      <c r="E8" t="str">
+        <v>XS-S</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>44</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-16 16:22:12</v>
+      </c>
+      <c r="C9" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Buso</v>
+      </c>
+      <c r="E9" t="str">
+        <v>L-XL</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>45</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-16 16:22:12</v>
+      </c>
+      <c r="C10" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Guayabera Diario</v>
+      </c>
+      <c r="E10" t="str">
+        <v>M-L</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>40</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-16 14:29:33</v>
+      </c>
+      <c r="C11" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>41</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-16 14:29:33</v>
+      </c>
+      <c r="C12" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Bermuda</v>
+      </c>
+      <c r="E12" t="str">
+        <v>12-14</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>42</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-16 14:29:33</v>
+      </c>
+      <c r="C13" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Buso</v>
+      </c>
+      <c r="E13" t="str">
+        <v>12-14</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>39</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-16 06:31:39</v>
+      </c>
+      <c r="C14" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E14" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>38</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-16 06:30:06</v>
+      </c>
+      <c r="C15" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E15" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>37</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-13 20:18:04</v>
+      </c>
+      <c r="C16" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>36</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-12 07:19:19</v>
+      </c>
+      <c r="C17" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E17" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>35</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-12 06:44:32</v>
+      </c>
+      <c r="C18" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Camisa Gala</v>
+      </c>
+      <c r="E18" t="str">
+        <v>M-L</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>34</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-06-12 06:36:20</v>
+      </c>
+      <c r="C19" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E19" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
         <v>33</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B20" t="str">
         <v>2026-06-12 06:31:22</v>
       </c>
-      <c r="C6" t="str">
-        <v>venta</v>
-      </c>
-      <c r="D6" t="str">
+      <c r="C20" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D20" t="str">
         <v>Pantalon</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E20" t="str">
         <v>10-12</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="str">
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="str">
         <v>Administrador</v>
       </c>
-      <c r="H6" t="str">
+      <c r="H20" t="str">
         <v>Venta registrada</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/movimientos.xlsx
+++ b/reportes/movimientos.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,16 +427,16 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-17 07:39:58</v>
+        <v>2026-06-25 07:46:40</v>
       </c>
       <c r="C2" t="str">
         <v>entrada</v>
       </c>
       <c r="D2" t="str">
-        <v>Pantalon</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E2" t="str">
         <v>10-12</v>
@@ -453,36 +453,36 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-16 20:39:32</v>
+        <v>2026-06-25 07:46:32</v>
       </c>
       <c r="C3" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D3" t="str">
-        <v>Pantalon</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E3" t="str">
         <v>10-12</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H3" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-16 20:39:20</v>
+        <v>2026-06-25 07:19:13</v>
       </c>
       <c r="C4" t="str">
         <v>venta</v>
@@ -505,16 +505,16 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-16 19:42:36</v>
+        <v>2026-06-22 14:24:03</v>
       </c>
       <c r="C5" t="str">
         <v>entrada</v>
       </c>
       <c r="D5" t="str">
-        <v>Pantalon</v>
+        <v>Sudadera 3 Piezas</v>
       </c>
       <c r="E5" t="str">
         <v>10-12</v>
@@ -531,45 +531,45 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-16 19:42:27</v>
+        <v>2026-06-22 14:23:24</v>
       </c>
       <c r="C6" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D6" t="str">
-        <v>Bata Azul</v>
+        <v>Sudadera 3 Piezas</v>
       </c>
       <c r="E6" t="str">
-        <v>Unica</v>
+        <v>10-12</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H6" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta bundle</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-16 16:32:55</v>
+        <v>2026-06-22 14:23:24</v>
       </c>
       <c r="C7" t="str">
         <v>venta</v>
       </c>
       <c r="D7" t="str">
-        <v>Bata Manga Larga</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E7" t="str">
-        <v>M-L</v>
+        <v>10-12</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -578,24 +578,24 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H7" t="str">
-        <v>Venta registrada</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-16 16:22:12</v>
+        <v>2026-06-22 14:23:24</v>
       </c>
       <c r="C8" t="str">
         <v>venta</v>
       </c>
       <c r="D8" t="str">
-        <v>Buso</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E8" t="str">
-        <v>XS-S</v>
+        <v>10-12</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -604,24 +604,24 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H8" t="str">
-        <v>Venta registrada</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-16 16:22:12</v>
+        <v>2026-06-22 14:23:24</v>
       </c>
       <c r="C9" t="str">
         <v>venta</v>
       </c>
       <c r="D9" t="str">
-        <v>Buso</v>
+        <v>Sudadera Pantalon</v>
       </c>
       <c r="E9" t="str">
-        <v>L-XL</v>
+        <v>10-12</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -630,24 +630,24 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H9" t="str">
-        <v>Venta registrada</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-16 16:22:12</v>
+        <v>2026-06-22 14:21:42</v>
       </c>
       <c r="C10" t="str">
         <v>venta</v>
       </c>
       <c r="D10" t="str">
-        <v>Guayabera Diario</v>
+        <v>Sudadera 3 Piezas</v>
       </c>
       <c r="E10" t="str">
-        <v>M-L</v>
+        <v>10-12</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -656,24 +656,24 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H10" t="str">
-        <v>Venta registrada</v>
+        <v>Venta bundle</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-16 14:29:33</v>
+        <v>2026-06-22 14:21:42</v>
       </c>
       <c r="C11" t="str">
         <v>venta</v>
       </c>
       <c r="D11" t="str">
-        <v>Bata Azul</v>
+        <v>Pantalon Colegial</v>
       </c>
       <c r="E11" t="str">
-        <v>Unica</v>
+        <v>12</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -682,24 +682,24 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H11" t="str">
-        <v>Venta registrada</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-16 14:29:33</v>
+        <v>2026-06-22 14:21:42</v>
       </c>
       <c r="C12" t="str">
         <v>venta</v>
       </c>
       <c r="D12" t="str">
-        <v>Bermuda</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E12" t="str">
-        <v>12-14</v>
+        <v>10-12</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -708,24 +708,24 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H12" t="str">
-        <v>Venta registrada</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-16 14:29:33</v>
+        <v>2026-06-22 14:21:42</v>
       </c>
       <c r="C13" t="str">
         <v>venta</v>
       </c>
       <c r="D13" t="str">
-        <v>Buso</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E13" t="str">
-        <v>12-14</v>
+        <v>10-12</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -734,151 +734,151 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H13" t="str">
-        <v>Venta registrada</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-16 06:31:39</v>
+        <v>2026-06-22 14:21:21</v>
       </c>
       <c r="C14" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D14" t="str">
-        <v>Pantalon</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E14" t="str">
         <v>10-12</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H14" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-16 06:30:06</v>
+        <v>2026-06-22 14:21:13</v>
       </c>
       <c r="C15" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D15" t="str">
-        <v>Pantalon</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E15" t="str">
         <v>10-12</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H15" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-13 20:18:04</v>
+        <v>2026-06-22 14:21:04</v>
       </c>
       <c r="C16" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D16" t="str">
-        <v>Bata Azul</v>
+        <v>Pantalon Colegial</v>
       </c>
       <c r="E16" t="str">
-        <v>Unica</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H16" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-12 07:19:19</v>
+        <v>2026-06-22 14:06:11</v>
       </c>
       <c r="C17" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D17" t="str">
-        <v>Pantalon</v>
+        <v>Pantalon Colegial</v>
       </c>
       <c r="E17" t="str">
-        <v>10-12</v>
+        <v>12</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H17" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-06-12 06:44:32</v>
+        <v>2026-06-22 14:06:11</v>
       </c>
       <c r="C18" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D18" t="str">
-        <v>Camisa Gala</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E18" t="str">
-        <v>M-L</v>
+        <v>10-12</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H18" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-06-12 06:36:20</v>
+        <v>2026-06-22 14:06:11</v>
       </c>
       <c r="C19" t="str">
         <v>venta</v>
       </c>
       <c r="D19" t="str">
-        <v>Pantalon</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E19" t="str">
         <v>10-12</v>
@@ -887,41 +887,951 @@
         <v>1</v>
       </c>
       <c r="G19" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H19" t="str">
-        <v>Venta registrada</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
+        <v>66</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-06-22 14:05:17</v>
+      </c>
+      <c r="C20" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Pantalon Colegial</v>
+      </c>
+      <c r="E20" t="str">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Venta como parte de bundle (x1)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>67</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-06-22 14:05:17</v>
+      </c>
+      <c r="C21" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Sudadera Pantaloneta</v>
+      </c>
+      <c r="E21" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Venta como parte de bundle (x1)</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>68</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-06-22 14:05:17</v>
+      </c>
+      <c r="C22" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Sudadera Camiseta</v>
+      </c>
+      <c r="E22" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Venta como parte de bundle (x1)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>65</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-06-22 06:49:47</v>
+      </c>
+      <c r="C23" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>64</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-06-22 06:48:49</v>
+      </c>
+      <c r="C24" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>63</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-06-19 15:37:06</v>
+      </c>
+      <c r="C25" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Sudadera 3 Piezas</v>
+      </c>
+      <c r="E25" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>62</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-06-19 15:27:54</v>
+      </c>
+      <c r="C26" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E26" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F26">
+        <v>10</v>
+      </c>
+      <c r="G26" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>61</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-06-19 15:27:08</v>
+      </c>
+      <c r="C27" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E27" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>60</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-06-19 15:26:39</v>
+      </c>
+      <c r="C28" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E28" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>59</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-06-19 14:38:28</v>
+      </c>
+      <c r="C29" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>58</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-06-19 14:34:54</v>
+      </c>
+      <c r="C30" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E30" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Venta #39</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>57</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-06-19 14:33:26</v>
+      </c>
+      <c r="C31" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E31" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Venta #38</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>56</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-06-19 14:32:46</v>
+      </c>
+      <c r="C32" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E32" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Venta #37</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>55</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-06-19 14:31:23</v>
+      </c>
+      <c r="C33" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E33" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Venta #36</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>54</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-06-19 14:27:50</v>
+      </c>
+      <c r="C34" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E34" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Venta #35</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>53</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-06-19 14:11:30</v>
+      </c>
+      <c r="C35" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E35" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Venta #34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>52</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-06-19 14:08:49</v>
+      </c>
+      <c r="C36" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E36" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Venta #33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>51</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-06-17 07:39:58</v>
+      </c>
+      <c r="C37" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E37" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>50</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-06-16 20:39:32</v>
+      </c>
+      <c r="C38" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E38" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>49</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-06-16 20:39:20</v>
+      </c>
+      <c r="C39" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E39" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>48</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-06-16 19:42:36</v>
+      </c>
+      <c r="C40" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E40" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>47</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-06-16 19:42:27</v>
+      </c>
+      <c r="C41" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>46</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-06-16 16:32:55</v>
+      </c>
+      <c r="C42" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Bata Manga Larga</v>
+      </c>
+      <c r="E42" t="str">
+        <v>M-L</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-06-16 16:22:12</v>
+      </c>
+      <c r="C43" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Buso</v>
+      </c>
+      <c r="E43" t="str">
+        <v>XS-S</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-06-16 16:22:12</v>
+      </c>
+      <c r="C44" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Buso</v>
+      </c>
+      <c r="E44" t="str">
+        <v>L-XL</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-06-16 16:22:12</v>
+      </c>
+      <c r="C45" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Guayabera Diario</v>
+      </c>
+      <c r="E45" t="str">
+        <v>M-L</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>40</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-06-16 14:29:33</v>
+      </c>
+      <c r="C46" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>41</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-06-16 14:29:33</v>
+      </c>
+      <c r="C47" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Bermuda</v>
+      </c>
+      <c r="E47" t="str">
+        <v>12-14</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>42</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-06-16 14:29:33</v>
+      </c>
+      <c r="C48" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Buso</v>
+      </c>
+      <c r="E48" t="str">
+        <v>12-14</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>39</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-06-16 06:31:39</v>
+      </c>
+      <c r="C49" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E49" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>38</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-06-16 06:30:06</v>
+      </c>
+      <c r="C50" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E50" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>37</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-06-13 20:18:04</v>
+      </c>
+      <c r="C51" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Bata Azul</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Unica</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>36</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-06-12 07:19:19</v>
+      </c>
+      <c r="C52" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E52" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>35</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-06-12 06:44:32</v>
+      </c>
+      <c r="C53" t="str">
+        <v>entrada</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Camisa Gala</v>
+      </c>
+      <c r="E53" t="str">
+        <v>M-L</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53" t="str">
+        <v>achinti morales hernández</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Entrada de stock</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>34</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-06-12 06:36:20</v>
+      </c>
+      <c r="C54" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E54" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
         <v>33</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B55" t="str">
         <v>2026-06-12 06:31:22</v>
       </c>
-      <c r="C20" t="str">
-        <v>venta</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Pantalon</v>
-      </c>
-      <c r="E20" t="str">
-        <v>10-12</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="str">
+      <c r="C55" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E55" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="str">
         <v>Administrador</v>
       </c>
-      <c r="H20" t="str">
+      <c r="H55" t="str">
         <v>Venta registrada</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H55"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reportes/movimientos.xlsx
+++ b/reportes/movimientos.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,42 +427,42 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-25 07:46:40</v>
+        <v>2026-06-25 15:29:41</v>
       </c>
       <c r="C2" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D2" t="str">
-        <v>Sudadera Pantaloneta</v>
+        <v>Pantalon</v>
       </c>
       <c r="E2" t="str">
         <v>10-12</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H2" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-25 07:46:32</v>
+        <v>2026-06-25 07:46:40</v>
       </c>
       <c r="C3" t="str">
         <v>entrada</v>
       </c>
       <c r="D3" t="str">
-        <v>Sudadera Camiseta</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E3" t="str">
         <v>10-12</v>
@@ -479,65 +479,65 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-25 07:19:13</v>
+        <v>2026-06-25 07:46:32</v>
       </c>
       <c r="C4" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D4" t="str">
-        <v>Pantalon</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E4" t="str">
         <v>10-12</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H4" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-22 14:24:03</v>
+        <v>2026-06-25 07:19:13</v>
       </c>
       <c r="C5" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D5" t="str">
-        <v>Sudadera 3 Piezas</v>
+        <v>Pantalon</v>
       </c>
       <c r="E5" t="str">
         <v>10-12</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H5" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-22 14:23:24</v>
+        <v>2026-06-22 14:24:03</v>
       </c>
       <c r="C6" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D6" t="str">
         <v>Sudadera 3 Piezas</v>
@@ -546,18 +546,18 @@
         <v>10-12</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H6" t="str">
-        <v>Venta bundle</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" t="str">
         <v>2026-06-22 14:23:24</v>
@@ -566,7 +566,7 @@
         <v>venta</v>
       </c>
       <c r="D7" t="str">
-        <v>Sudadera Pantaloneta</v>
+        <v>Sudadera 3 Piezas</v>
       </c>
       <c r="E7" t="str">
         <v>10-12</v>
@@ -578,12 +578,12 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H7" t="str">
-        <v>Venta como parte de bundle (x1)</v>
+        <v>Venta bundle</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" t="str">
         <v>2026-06-22 14:23:24</v>
@@ -592,7 +592,7 @@
         <v>venta</v>
       </c>
       <c r="D8" t="str">
-        <v>Sudadera Camiseta</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E8" t="str">
         <v>10-12</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" t="str">
         <v>2026-06-22 14:23:24</v>
@@ -618,7 +618,7 @@
         <v>venta</v>
       </c>
       <c r="D9" t="str">
-        <v>Sudadera Pantalon</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E9" t="str">
         <v>10-12</v>
@@ -635,16 +635,16 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-22 14:21:42</v>
+        <v>2026-06-22 14:23:24</v>
       </c>
       <c r="C10" t="str">
         <v>venta</v>
       </c>
       <c r="D10" t="str">
-        <v>Sudadera 3 Piezas</v>
+        <v>Sudadera Pantalon</v>
       </c>
       <c r="E10" t="str">
         <v>10-12</v>
@@ -656,12 +656,12 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H10" t="str">
-        <v>Venta bundle</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" t="str">
         <v>2026-06-22 14:21:42</v>
@@ -670,10 +670,10 @@
         <v>venta</v>
       </c>
       <c r="D11" t="str">
-        <v>Pantalon Colegial</v>
+        <v>Sudadera 3 Piezas</v>
       </c>
       <c r="E11" t="str">
-        <v>12</v>
+        <v>10-12</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -682,12 +682,12 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H11" t="str">
-        <v>Venta como parte de bundle (x1)</v>
+        <v>Venta bundle</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" t="str">
         <v>2026-06-22 14:21:42</v>
@@ -696,10 +696,10 @@
         <v>venta</v>
       </c>
       <c r="D12" t="str">
-        <v>Sudadera Pantaloneta</v>
+        <v>Pantalon Colegial</v>
       </c>
       <c r="E12" t="str">
-        <v>10-12</v>
+        <v>12</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" t="str">
         <v>2026-06-22 14:21:42</v>
@@ -722,7 +722,7 @@
         <v>venta</v>
       </c>
       <c r="D13" t="str">
-        <v>Sudadera Camiseta</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E13" t="str">
         <v>10-12</v>
@@ -739,42 +739,42 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-22 14:21:21</v>
+        <v>2026-06-22 14:21:42</v>
       </c>
       <c r="C14" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D14" t="str">
-        <v>Sudadera Pantaloneta</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E14" t="str">
         <v>10-12</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H14" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-22 14:21:13</v>
+        <v>2026-06-22 14:21:21</v>
       </c>
       <c r="C15" t="str">
         <v>entrada</v>
       </c>
       <c r="D15" t="str">
-        <v>Sudadera Camiseta</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E15" t="str">
         <v>10-12</v>
@@ -791,19 +791,19 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-06-22 14:21:04</v>
+        <v>2026-06-22 14:21:13</v>
       </c>
       <c r="C16" t="str">
         <v>entrada</v>
       </c>
       <c r="D16" t="str">
-        <v>Pantalon Colegial</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E16" t="str">
-        <v>12</v>
+        <v>10-12</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -817,13 +817,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-06-22 14:06:11</v>
+        <v>2026-06-22 14:21:04</v>
       </c>
       <c r="C17" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D17" t="str">
         <v>Pantalon Colegial</v>
@@ -832,18 +832,18 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H17" t="str">
-        <v>Venta como parte de bundle (x1)</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" t="str">
         <v>2026-06-22 14:06:11</v>
@@ -852,10 +852,10 @@
         <v>venta</v>
       </c>
       <c r="D18" t="str">
-        <v>Sudadera Pantaloneta</v>
+        <v>Pantalon Colegial</v>
       </c>
       <c r="E18" t="str">
-        <v>10-12</v>
+        <v>12</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19" t="str">
         <v>2026-06-22 14:06:11</v>
@@ -878,7 +878,7 @@
         <v>venta</v>
       </c>
       <c r="D19" t="str">
-        <v>Sudadera Camiseta</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E19" t="str">
         <v>10-12</v>
@@ -895,19 +895,19 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B20" t="str">
-        <v>2026-06-22 14:05:17</v>
+        <v>2026-06-22 14:06:11</v>
       </c>
       <c r="C20" t="str">
         <v>venta</v>
       </c>
       <c r="D20" t="str">
-        <v>Pantalon Colegial</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E20" t="str">
-        <v>12</v>
+        <v>10-12</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" t="str">
         <v>2026-06-22 14:05:17</v>
@@ -930,10 +930,10 @@
         <v>venta</v>
       </c>
       <c r="D21" t="str">
-        <v>Sudadera Pantaloneta</v>
+        <v>Pantalon Colegial</v>
       </c>
       <c r="E21" t="str">
-        <v>10-12</v>
+        <v>12</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -947,7 +947,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" t="str">
         <v>2026-06-22 14:05:17</v>
@@ -956,7 +956,7 @@
         <v>venta</v>
       </c>
       <c r="D22" t="str">
-        <v>Sudadera Camiseta</v>
+        <v>Sudadera Pantaloneta</v>
       </c>
       <c r="E22" t="str">
         <v>10-12</v>
@@ -973,39 +973,39 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-06-22 06:49:47</v>
+        <v>2026-06-22 14:05:17</v>
       </c>
       <c r="C23" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D23" t="str">
-        <v>Bata Azul</v>
+        <v>Sudadera Camiseta</v>
       </c>
       <c r="E23" t="str">
-        <v>Unica</v>
+        <v>10-12</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G23" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H23" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta como parte de bundle (x1)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-06-22 06:48:49</v>
+        <v>2026-06-22 06:49:47</v>
       </c>
       <c r="C24" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D24" t="str">
         <v>Bata Azul</v>
@@ -1014,33 +1014,33 @@
         <v>Unica</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H24" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" t="str">
-        <v>2026-06-19 15:37:06</v>
+        <v>2026-06-22 06:48:49</v>
       </c>
       <c r="C25" t="str">
         <v>venta</v>
       </c>
       <c r="D25" t="str">
-        <v>Sudadera 3 Piezas</v>
+        <v>Bata Azul</v>
       </c>
       <c r="E25" t="str">
-        <v>10-12</v>
+        <v>Unica</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G25" t="str">
         <v>achinti morales hernández</v>
@@ -1051,39 +1051,39 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" t="str">
-        <v>2026-06-19 15:27:54</v>
+        <v>2026-06-19 15:37:06</v>
       </c>
       <c r="C26" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D26" t="str">
-        <v>Pantalon</v>
+        <v>Sudadera 3 Piezas</v>
       </c>
       <c r="E26" t="str">
         <v>10-12</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G26" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H26" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-06-19 15:27:08</v>
+        <v>2026-06-19 15:27:54</v>
       </c>
       <c r="C27" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D27" t="str">
         <v>Pantalon</v>
@@ -1092,21 +1092,21 @@
         <v>10-12</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G27" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H27" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B28" t="str">
-        <v>2026-06-19 15:26:39</v>
+        <v>2026-06-19 15:27:08</v>
       </c>
       <c r="C28" t="str">
         <v>venta</v>
@@ -1129,19 +1129,19 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B29" t="str">
-        <v>2026-06-19 14:38:28</v>
+        <v>2026-06-19 15:26:39</v>
       </c>
       <c r="C29" t="str">
         <v>venta</v>
       </c>
       <c r="D29" t="str">
-        <v>Bata Azul</v>
+        <v>Pantalon</v>
       </c>
       <c r="E29" t="str">
-        <v>Unica</v>
+        <v>10-12</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -1155,19 +1155,19 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-06-19 14:34:54</v>
+        <v>2026-06-19 14:38:28</v>
       </c>
       <c r="C30" t="str">
         <v>venta</v>
       </c>
       <c r="D30" t="str">
-        <v>Pantalon</v>
+        <v>Bata Azul</v>
       </c>
       <c r="E30" t="str">
-        <v>10-12</v>
+        <v>Unica</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -1176,15 +1176,15 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H30" t="str">
-        <v>Venta #39</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B31" t="str">
-        <v>2026-06-19 14:33:26</v>
+        <v>2026-06-19 14:34:54</v>
       </c>
       <c r="C31" t="str">
         <v>venta</v>
@@ -1202,15 +1202,15 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H31" t="str">
-        <v>Venta #38</v>
+        <v>Venta #39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B32" t="str">
-        <v>2026-06-19 14:32:46</v>
+        <v>2026-06-19 14:33:26</v>
       </c>
       <c r="C32" t="str">
         <v>venta</v>
@@ -1228,15 +1228,15 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H32" t="str">
-        <v>Venta #37</v>
+        <v>Venta #38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33" t="str">
-        <v>2026-06-19 14:31:23</v>
+        <v>2026-06-19 14:32:46</v>
       </c>
       <c r="C33" t="str">
         <v>venta</v>
@@ -1254,15 +1254,15 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H33" t="str">
-        <v>Venta #36</v>
+        <v>Venta #37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-06-19 14:27:50</v>
+        <v>2026-06-19 14:31:23</v>
       </c>
       <c r="C34" t="str">
         <v>venta</v>
@@ -1280,15 +1280,15 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H34" t="str">
-        <v>Venta #35</v>
+        <v>Venta #36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-06-19 14:11:30</v>
+        <v>2026-06-19 14:27:50</v>
       </c>
       <c r="C35" t="str">
         <v>venta</v>
@@ -1306,15 +1306,15 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H35" t="str">
-        <v>Venta #34</v>
+        <v>Venta #35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-06-19 14:08:49</v>
+        <v>2026-06-19 14:11:30</v>
       </c>
       <c r="C36" t="str">
         <v>venta</v>
@@ -1332,18 +1332,18 @@
         <v>achinti morales hernández</v>
       </c>
       <c r="H36" t="str">
-        <v>Venta #33</v>
+        <v>Venta #34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-06-17 07:39:58</v>
+        <v>2026-06-19 14:08:49</v>
       </c>
       <c r="C37" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D37" t="str">
         <v>Pantalon</v>
@@ -1352,24 +1352,24 @@
         <v>10-12</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H37" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta #33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-06-16 20:39:32</v>
+        <v>2026-06-17 07:39:58</v>
       </c>
       <c r="C38" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D38" t="str">
         <v>Pantalon</v>
@@ -1378,21 +1378,21 @@
         <v>10-12</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H38" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-06-16 20:39:20</v>
+        <v>2026-06-16 20:39:32</v>
       </c>
       <c r="C39" t="str">
         <v>venta</v>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-06-16 19:42:36</v>
+        <v>2026-06-16 20:39:20</v>
       </c>
       <c r="C40" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D40" t="str">
         <v>Pantalon</v>
@@ -1430,30 +1430,30 @@
         <v>10-12</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H40" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-06-16 19:42:27</v>
+        <v>2026-06-16 19:42:36</v>
       </c>
       <c r="C41" t="str">
         <v>entrada</v>
       </c>
       <c r="D41" t="str">
-        <v>Bata Azul</v>
+        <v>Pantalon</v>
       </c>
       <c r="E41" t="str">
-        <v>Unica</v>
+        <v>10-12</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -1467,45 +1467,45 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-06-16 16:32:55</v>
+        <v>2026-06-16 19:42:27</v>
       </c>
       <c r="C42" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D42" t="str">
-        <v>Bata Manga Larga</v>
+        <v>Bata Azul</v>
       </c>
       <c r="E42" t="str">
-        <v>M-L</v>
+        <v>Unica</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="str">
         <v>achinti morales hernández</v>
       </c>
       <c r="H42" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-06-16 16:22:12</v>
+        <v>2026-06-16 16:32:55</v>
       </c>
       <c r="C43" t="str">
         <v>venta</v>
       </c>
       <c r="D43" t="str">
-        <v>Buso</v>
+        <v>Bata Manga Larga</v>
       </c>
       <c r="E43" t="str">
-        <v>XS-S</v>
+        <v>M-L</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" t="str">
         <v>2026-06-16 16:22:12</v>
@@ -1531,7 +1531,7 @@
         <v>Buso</v>
       </c>
       <c r="E44" t="str">
-        <v>L-XL</v>
+        <v>XS-S</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" t="str">
         <v>2026-06-16 16:22:12</v>
@@ -1554,10 +1554,10 @@
         <v>venta</v>
       </c>
       <c r="D45" t="str">
-        <v>Guayabera Diario</v>
+        <v>Buso</v>
       </c>
       <c r="E45" t="str">
-        <v>M-L</v>
+        <v>L-XL</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -1571,19 +1571,19 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>2026-06-16 14:29:33</v>
+        <v>2026-06-16 16:22:12</v>
       </c>
       <c r="C46" t="str">
         <v>venta</v>
       </c>
       <c r="D46" t="str">
-        <v>Bata Azul</v>
+        <v>Guayabera Diario</v>
       </c>
       <c r="E46" t="str">
-        <v>Unica</v>
+        <v>M-L</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="str">
         <v>2026-06-16 14:29:33</v>
@@ -1606,10 +1606,10 @@
         <v>venta</v>
       </c>
       <c r="D47" t="str">
-        <v>Bermuda</v>
+        <v>Bata Azul</v>
       </c>
       <c r="E47" t="str">
-        <v>12-14</v>
+        <v>Unica</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" t="str">
         <v>2026-06-16 14:29:33</v>
@@ -1632,7 +1632,7 @@
         <v>venta</v>
       </c>
       <c r="D48" t="str">
-        <v>Buso</v>
+        <v>Bermuda</v>
       </c>
       <c r="E48" t="str">
         <v>12-14</v>
@@ -1649,19 +1649,19 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B49" t="str">
-        <v>2026-06-16 06:31:39</v>
+        <v>2026-06-16 14:29:33</v>
       </c>
       <c r="C49" t="str">
         <v>venta</v>
       </c>
       <c r="D49" t="str">
-        <v>Pantalon</v>
+        <v>Buso</v>
       </c>
       <c r="E49" t="str">
-        <v>10-12</v>
+        <v>12-14</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B50" t="str">
-        <v>2026-06-16 06:30:06</v>
+        <v>2026-06-16 06:31:39</v>
       </c>
       <c r="C50" t="str">
         <v>venta</v>
@@ -1701,25 +1701,25 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B51" t="str">
-        <v>2026-06-13 20:18:04</v>
+        <v>2026-06-16 06:30:06</v>
       </c>
       <c r="C51" t="str">
         <v>venta</v>
       </c>
       <c r="D51" t="str">
-        <v>Bata Azul</v>
+        <v>Pantalon</v>
       </c>
       <c r="E51" t="str">
-        <v>Unica</v>
+        <v>10-12</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H51" t="str">
         <v>Venta registrada</v>
@@ -1727,51 +1727,51 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B52" t="str">
-        <v>2026-06-12 07:19:19</v>
+        <v>2026-06-13 20:18:04</v>
       </c>
       <c r="C52" t="str">
-        <v>entrada</v>
+        <v>venta</v>
       </c>
       <c r="D52" t="str">
-        <v>Pantalon</v>
+        <v>Bata Azul</v>
       </c>
       <c r="E52" t="str">
-        <v>10-12</v>
+        <v>Unica</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="str">
         <v>Administrador</v>
       </c>
       <c r="H52" t="str">
-        <v>Entrada de stock</v>
+        <v>Venta registrada</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B53" t="str">
-        <v>2026-06-12 06:44:32</v>
+        <v>2026-06-12 07:19:19</v>
       </c>
       <c r="C53" t="str">
         <v>entrada</v>
       </c>
       <c r="D53" t="str">
-        <v>Camisa Gala</v>
+        <v>Pantalon</v>
       </c>
       <c r="E53" t="str">
-        <v>M-L</v>
+        <v>10-12</v>
       </c>
       <c r="F53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G53" t="str">
-        <v>achinti morales hernández</v>
+        <v>Administrador</v>
       </c>
       <c r="H53" t="str">
         <v>Entrada de stock</v>
@@ -1779,36 +1779,36 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B54" t="str">
-        <v>2026-06-12 06:36:20</v>
+        <v>2026-06-12 06:44:32</v>
       </c>
       <c r="C54" t="str">
-        <v>venta</v>
+        <v>entrada</v>
       </c>
       <c r="D54" t="str">
-        <v>Pantalon</v>
+        <v>Camisa Gala</v>
       </c>
       <c r="E54" t="str">
-        <v>10-12</v>
+        <v>M-L</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G54" t="str">
-        <v>Administrador</v>
+        <v>achinti morales hernández</v>
       </c>
       <c r="H54" t="str">
-        <v>Venta registrada</v>
+        <v>Entrada de stock</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B55" t="str">
-        <v>2026-06-12 06:31:22</v>
+        <v>2026-06-12 06:36:20</v>
       </c>
       <c r="C55" t="str">
         <v>venta</v>
@@ -1829,9 +1829,35 @@
         <v>Venta registrada</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56">
+        <v>33</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2026-06-12 06:31:22</v>
+      </c>
+      <c r="C56" t="str">
+        <v>venta</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Pantalon</v>
+      </c>
+      <c r="E56" t="str">
+        <v>10-12</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Administrador</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Venta registrada</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H56"/>
   </ignoredErrors>
 </worksheet>
 </file>